--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261022.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261022.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.6388429752066116</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.0178264462809917</v>
+        <v>0.0244380165289256</v>
       </c>
     </row>
     <row r="8">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>対象先の選定</t>
+          <t>依頼の送付・日程調整</t>
         </is>
       </c>
       <c r="D2" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E2" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F2" s="19" t="inlineStr">
@@ -3171,9 +3171,9 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="G2" s="25" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G2" s="23" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="H2" s="30" t="n">
@@ -3186,7 +3186,7 @@
         <v>-100</v>
       </c>
       <c r="K2" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" s="23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="M2" s="18" t="inlineStr">
         <is>
-          <t>**町のサービス実績（町内外事業所別・依頼票D4）**</t>
+          <t>対象先の選定</t>
         </is>
       </c>
     </row>
@@ -3207,12 +3207,12 @@
       </c>
       <c r="B3" s="19" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>依頼の送付・日程調整</t>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
       <c r="D3" s="19" t="inlineStr">
@@ -3227,34 +3227,34 @@
       </c>
       <c r="F3" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G3" s="25" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G3" s="23" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="H3" s="30" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="30" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J3" s="30" t="n">
-        <v>-100</v>
+        <v>-85</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="23" t="inlineStr">
-        <is>
-          <t>期限超過（1か月）</t>
+        <v>4</v>
+      </c>
+      <c r="L3" s="24" t="inlineStr">
+        <is>
+          <t>遅れ</t>
         </is>
       </c>
       <c r="M3" s="18" t="inlineStr">
         <is>
-          <t>対象先の選定</t>
+          <t>日程調整</t>
         </is>
       </c>
     </row>
@@ -3266,54 +3266,54 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>対象先の選定</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G4" s="25" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="H4" s="30" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I4" s="30" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="J4" s="30" t="n">
-        <v>-85</v>
+        <v>-70</v>
       </c>
       <c r="K4" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" s="24" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+        <v>2</v>
+      </c>
+      <c r="L4" s="23" t="inlineStr">
+        <is>
+          <t>期限超過（1か月）</t>
         </is>
       </c>
       <c r="M4" s="18" t="inlineStr">
         <is>
-          <t>日程調整</t>
+          <t>**町のサービス実績（町内外事業所別・依頼票D4）**</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>2-11</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>骨子案の協議（自立支援協議会）</t>
+          <t>集計・分析</t>
         </is>
       </c>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G42" s="22" t="inlineStr">
@@ -5537,16 +5537,16 @@
         </is>
       </c>
       <c r="H42" s="30" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I42" s="30" t="n">
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="J42" s="30" t="n">
-        <v>20</v>
+        <v>28.3</v>
       </c>
       <c r="K42" s="19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="31" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="M42" s="18" t="inlineStr">
         <is>
-          <t>工程変更の合意</t>
+          <t>**レビュー所見の反映（重大5件）。**うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5567,12 @@
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>2-11</t>
+          <t>2-12</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>集計・分析</t>
+          <t>分析報告書のレビュー</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
@@ -5582,27 +5582,27 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="F43" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="G43" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H43" s="30" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="I43" s="30" t="n">
-        <v>56.7</v>
+        <v>70</v>
       </c>
       <c r="J43" s="30" t="n">
-        <v>28.3</v>
+        <v>30</v>
       </c>
       <c r="K43" s="19" t="n">
         <v>3</v>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M43" s="18" t="inlineStr">
         <is>
-          <t>**レビュー所見の反映（重大5件）。**うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>2-12</t>
+          <t>2-13</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>分析報告書のレビュー</t>
+          <t>目標値とアンケート設問の対応（MECEチェック）</t>
         </is>
       </c>
       <c r="D44" s="19" t="inlineStr">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>2-13</t>
+          <t>2-14</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>目標値とアンケート設問の対応（MECEチェック）</t>
+          <t>アンケートで不足する事項の洗い出しと対応方針</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
@@ -5744,12 +5744,12 @@
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>2-14</t>
+          <t>2-16</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>アンケートで不足する事項の洗い出しと対応方針</t>
+          <t>確認票の2枚化（町向け・事業所向け）</t>
         </is>
       </c>
       <c r="D46" s="19" t="inlineStr">
@@ -5782,7 +5782,7 @@
         <v>30</v>
       </c>
       <c r="K46" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L46" s="31" t="inlineStr">
         <is>
@@ -5798,44 +5798,44 @@
     <row r="47">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
-          <t>2-16</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>確認票の2枚化（町向け・事業所向け）</t>
+          <t>骨子案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F47" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G47" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H47" s="30" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I47" s="30" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J47" s="30" t="n">
         <v>30</v>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="M47" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>工程変更の合意</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
     <row r="52">
       <c r="A52" s="32" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 63.9％　対　予定進捗率 62.1％　乖離 +1.8ポイント</t>
+          <t>加重の実績進捗率 64.5％　対　予定進捗率 62.1％　乖離 +2.4ポイント</t>
         </is>
       </c>
     </row>
@@ -8010,20 +8010,20 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K26" s="25" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="L26" s="21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M26" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N26" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**10月22日、訪問ヒアリングに代えて、公表資料（情報公表データ・県の圏域計画）、第2回自立支援協議会での意見聴取、町が日頃把握している情報で置き換える代替案を作成した（15_ヒアリング・調査設計）。町の了解待ち。**</t>
         </is>
       </c>
       <c r="O26" s="18" t="inlineStr">
@@ -8083,9 +8083,9 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K27" s="25" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="L27" s="21" t="n">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="N27" s="18" t="inlineStr">
         <is>
-          <t>依頼文の記載事項は実施計画書に整理</t>
+          <t>**代替案では依頼の送付は行わない（町の了解待ち）。**依頼文の記載事項は実施計画書に整理</t>
         </is>
       </c>
       <c r="O27" s="18" t="inlineStr">
@@ -8156,9 +8156,9 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K28" s="25" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="L28" s="21" t="n">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="N28" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**代替案では第2回自立支援協議会（11月下旬）での意見聴取に置き換える。**</t>
         </is>
       </c>
       <c r="O28" s="18" t="inlineStr">
@@ -8893,14 +8893,14 @@
         </is>
       </c>
       <c r="L38" s="21" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M38" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N38" s="18" t="inlineStr">
         <is>
-          <t>**10月21日に第2回自立支援協議会資料（案）と想定問答集（事務局用・33問）を作成した。開催日は未定。****仕様書7では10月の回。工程変更により12月に統合する案を協議中**</t>
+          <t>**第2回自立支援協議会は令和8年11月下旬に開催予定（10月22日に町から）。資料（案）と想定問答集を作成済み。****仕様書7では10月の回。工程変更により12月に統合する案を協議中**</t>
         </is>
       </c>
       <c r="O38" s="18" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261022.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261022.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.6454545454545455</v>
+        <v>0.6487603305785125</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.0244380165289256</v>
+        <v>0.02774380165289259</v>
       </c>
     </row>
     <row r="8">
@@ -3171,9 +3171,9 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="G2" s="23" t="inlineStr">
-        <is>
-          <t>要対応</t>
+      <c r="G2" s="25" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H2" s="30" t="n">
@@ -3230,9 +3230,9 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="G3" s="23" t="inlineStr">
-        <is>
-          <t>要対応</t>
+      <c r="G3" s="25" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H3" s="30" t="n">
@@ -3261,22 +3261,22 @@
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>対象先の選定</t>
+          <t>町データの受領</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E4" s="19" t="inlineStr">
@@ -3289,22 +3289,22 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
-        <is>
-          <t>要対応</t>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H4" s="30" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I4" s="30" t="n">
         <v>100</v>
       </c>
       <c r="J4" s="30" t="n">
-        <v>-70</v>
+        <v>-60</v>
       </c>
       <c r="K4" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4" s="23" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="M4" s="18" t="inlineStr">
         <is>
-          <t>**町のサービス実績（町内外事業所別・依頼票D4）**</t>
+          <t>**町の回答。P2・P5・P6が依存する**</t>
         </is>
       </c>
     </row>
@@ -3325,17 +3325,17 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>1-7</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>町データの受領</t>
+          <t>工程変更の協議と打合せ記録の作成</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E5" s="19" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G5" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="H5" s="30" t="n">
@@ -3363,33 +3363,33 @@
         <v>-60</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L5" s="23" t="inlineStr">
         <is>
-          <t>期限超過（1か月）</t>
+          <t>期限超過（2か月）</t>
         </is>
       </c>
       <c r="M5" s="18" t="inlineStr">
         <is>
-          <t>**町の回答。P2・P5・P6が依存する**</t>
+          <t>**町との協議。8月19日の協議会またはその前後に行う**</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>1-7</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>工程変更の協議と打合せ記録の作成</t>
+          <t>対象先の選定</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
@@ -3404,34 +3404,34 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H6" s="30" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I6" s="30" t="n">
         <v>100</v>
       </c>
       <c r="J6" s="30" t="n">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="K6" s="19" t="n">
         <v>2</v>
       </c>
       <c r="L6" s="23" t="inlineStr">
         <is>
-          <t>期限超過（2か月）</t>
+          <t>期限超過（1か月）</t>
         </is>
       </c>
       <c r="M6" s="18" t="inlineStr">
         <is>
-          <t>**町との協議。8月19日の協議会またはその前後に行う**</t>
+          <t>**町のサービス実績（町内外事業所別・依頼票D4）**</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
     <row r="52">
       <c r="A52" s="32" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 64.5％　対　予定進捗率 62.1％　乖離 +2.4ポイント</t>
+          <t>加重の実績進捗率 64.9％　対　予定進捗率 62.1％　乖離 +2.8ポイント</t>
         </is>
       </c>
     </row>
@@ -8010,20 +8010,20 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K26" s="23" t="inlineStr">
-        <is>
-          <t>要対応</t>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L26" s="21" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="M26" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N26" s="18" t="inlineStr">
         <is>
-          <t>**10月22日、訪問ヒアリングに代えて、公表資料（情報公表データ・県の圏域計画）、第2回自立支援協議会での意見聴取、町が日頃把握している情報で置き換える代替案を作成した（15_ヒアリング・調査設計）。町の了解待ち。**</t>
+          <t>**10月22日、仕様書どおり事業所ヒアリングを行う方針とし、質問35問を公表データ・町のデータで確認できるもの（11問）と当日伺うもの（24問）に仕分けた。ヒアリングシートと対象先の候補（町内7・田村地方72）を作成した（15_ヒアリング・調査設計）。町外の対象先は町の利用データで確定する。**</t>
         </is>
       </c>
       <c r="O26" s="18" t="inlineStr">
@@ -8083,9 +8083,9 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K27" s="23" t="inlineStr">
-        <is>
-          <t>要対応</t>
+      <c r="K27" s="25" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="L27" s="21" t="n">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="N27" s="18" t="inlineStr">
         <is>
-          <t>**代替案では依頼の送付は行わない（町の了解待ち）。**依頼文の記載事項は実施計画書に整理</t>
+          <t>**ヒアリングシートは作成済み。依頼文の名義と送付方法を町に確認中。11月上旬に送付予定。**依頼文の記載事項は実施計画書に整理</t>
         </is>
       </c>
       <c r="O27" s="18" t="inlineStr">
@@ -8156,9 +8156,9 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K28" s="23" t="inlineStr">
-        <is>
-          <t>要対応</t>
+      <c r="K28" s="25" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="L28" s="21" t="n">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="N28" s="18" t="inlineStr">
         <is>
-          <t>**代替案では第2回自立支援協議会（11月下旬）での意見聴取に置き換える。**</t>
+          <t>**11月上旬〜中旬に実施予定（30分程度。訪問・電話・オンライン）。結果は第2回自立支援協議会で報告。**</t>
         </is>
       </c>
       <c r="O28" s="18" t="inlineStr">
